--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlSkill.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlSkill.xlsx
@@ -5,11 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="BrawlSkill" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="工作表2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="BrawProjectile" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="76">
   <si>
     <t xml:space="preserve">##var</t>
   </si>
@@ -41,28 +41,62 @@
     <t xml:space="preserve">ProjectileCount</t>
   </si>
   <si>
-    <t xml:space="preserve">Shecheng</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Zhuangtiansudu</t>
+    <t xml:space="preserve">CDTime</t>
   </si>
   <si>
     <t xml:space="preserve">SkillType</t>
   </si>
   <si>
-    <t xml:space="preserve">SpecialSkillId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BaseHp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HpGrowthPerLevel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MoveSpeedTier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">UnlockPrice</t>
+    <t xml:space="preserve">SkillRangeType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkillRangeParam1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Skill</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">Range</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Param2</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">SkillCastRangeType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkillCastParam1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkillCastParam2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkillEmmiterType</t>
   </si>
   <si>
     <t xml:space="preserve">##type</t>
@@ -95,27 +129,214 @@
     <t xml:space="preserve">描述</t>
   </si>
   <si>
-    <t xml:space="preserve">子弹 ID</t>
+    <t xml:space="preserve">  抛射体   ID</t>
   </si>
   <si>
     <t xml:space="preserve">子弹数量</t>
   </si>
   <si>
-    <t xml:space="preserve">射程</t>
-  </si>
-  <si>
     <t xml:space="preserve">装弹时间</t>
   </si>
   <si>
+    <t xml:space="preserve">技能类型
+1 预留，可能废弃
+2 
+3 
+4 </t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">技能范围类型 </t>
+    </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color rgb="FF222222"/>
         <rFont val="Microsoft YaHei"/>
         <family val="0"/>
+      </rPr>
+      <t xml:space="preserve"> 
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">技能类型
+      <t xml:space="preserve">1 矩形
+2 扇形
+3 圆形</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">技能范围参数1</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">技能</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">范围</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">参数2，有参数1的时候，参数2才有效</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">技能施放范围类型等于0就用</t>
+    </r>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">SkillRangeType
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1 矩形
+2 扇形
+3 圆形</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">技能施放参数1
+等于0 没有距离，原地释放
+大于0 有抛物线/矩形等 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">技能施放参数2，有参数1的时候，参数2才有效</t>
+  </si>
+  <si>
+    <t xml:space="preserve">技能发射器类型</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大口径霰弹枪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雪莉的霰弹枪可大范围射出多枚射程较远的弹丸，命中敌人的弹丸越多，造成的伤害越高。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">公牛普通攻击</t>
+  </si>
+  <si>
+    <t xml:space="preserve">连续发射2次</t>
+  </si>
+  <si>
+    <t xml:space="preserve">卡尔普通攻击</t>
+  </si>
+  <si>
+    <t xml:space="preserve">卡尔丢出回旋镖</t>
+  </si>
+  <si>
+    <t xml:space="preserve">武士普通攻击</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用小刀捅2下.且发出强劲的刀风。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">左轮手枪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柯尔特使用它的左轮手枪向同一方向连开6枪，可攻击到远距离的的人。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">子弹风暴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柯尔特迅速开火，射出大量子弹，这些子弹的射程更远且能摧毁掩体。</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CollisionDestroyedCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ValueGrowthPerLevel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CollisionEvent1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CollisionEventParam1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CollisionEventParam2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CollisionEvent2</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+      </rPr>
+      <t xml:space="preserve">有效目标
 </t>
     </r>
     <r>
@@ -125,71 +346,60 @@
         <rFont val="Microsoft YaHei"/>
         <family val="0"/>
       </rPr>
-      <t xml:space="preserve">1 近战 
-2 
-3 快
-4 非常快</t>
+      <t xml:space="preserve">0 无
+1 敌方
+2 友方
+4 可摧毁墙体
+8 可摧毁草</t>
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF222222"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">特殊技能ID</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF222222"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">1 慢
-2 中
-3 快
-4 非常快</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">1 级基础生命值
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">每升一级增加的生命值
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">移速档位，不是实际速度 
-1 慢
-2 中
-3 快
-4 非常快</t>
-  </si>
-  <si>
-    <t xml:space="preserve">解锁价格</t>
-  </si>
-  <si>
-    <t xml:space="preserve">大口径霰弹枪</t>
-  </si>
-  <si>
-    <t xml:space="preserve">雪莉的霰弹枪可大范围射出多枚射程较远的弹丸，命中敌人的弹丸越多，造成的伤害越高。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公牛</t>
-  </si>
-  <si>
-    <t xml:space="preserve">公牛没有年轻时那么无忧无虑，也没有那么爱惹事了。但如果有人敢挑衅，他还是会毫不犹豫地把他们撞飞！</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BasicMaleDefault</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> </t>
+    <t xml:space="preserve">耐久度，即碰撞几次再销毁，一般需要碰到有效目标才算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">持续时间</t>
+  </si>
+  <si>
+    <t xml:space="preserve">速度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">基础数值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">额外数值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">碰撞事件1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">碰撞事件1参数1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">碰撞事件1参数2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">碰撞事件2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">碰撞事件2参数1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">碰撞事件2参数2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雪莉的霰弹枪的子弹</t>
+  </si>
+  <si>
+    <t xml:space="preserve">卡尔丢出的回旋镖</t>
+  </si>
+  <si>
+    <t xml:space="preserve">武士的小刀效果</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柯尔特的手枪子弹</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柯尔特的大招子弹</t>
   </si>
 </sst>
 </file>
@@ -199,7 +409,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <sz val="10"/>
       <name val="Noto Sans SC"/>
@@ -258,6 +468,13 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF222222"/>
+      <name val="Microsoft YaHei"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF222222"/>
       <name val="Microsoft YaHei"/>
@@ -268,7 +485,13 @@
       <color rgb="FF222222"/>
       <name val="Microsoft YaHei"/>
       <family val="0"/>
-      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF222222"/>
+      <name val="Microsoft YaHei"/>
+      <family val="0"/>
     </font>
   </fonts>
   <fills count="5">
@@ -335,7 +558,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -360,10 +583,6 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -380,11 +599,19 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -635,18 +862,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD22"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="2" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="6" style="1" width="16.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="9" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="26.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16382" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="8" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="13" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16383" min="16379" style="0" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -668,16 +896,16 @@
       <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>6</v>
       </c>
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="5" t="s">
         <v>9</v>
       </c>
       <c r="K1" s="5" t="s">
@@ -692,115 +920,125 @@
       <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="B2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="C2" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="I2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="M2" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="N2" s="7" t="s">
-        <v>15</v>
+      <c r="G2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" s="8"/>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
-      <c r="M3" s="7"/>
-      <c r="N3" s="7"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="121.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="B4" s="9" t="s">
+      <c r="A4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="C4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="C4" s="8" t="s">
         <v>23</v>
       </c>
+      <c r="D4" s="9" t="s">
+        <v>24</v>
+      </c>
       <c r="E4" s="10" t="s">
-        <v>24</v>
-      </c>
-      <c r="F4" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="F4" s="9" t="s">
         <v>26</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="G4" s="9" t="s">
         <v>27</v>
       </c>
+      <c r="H4" s="9" t="s">
+        <v>28</v>
+      </c>
       <c r="I4" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J4" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="L4" s="11" t="s">
+      <c r="K4" s="10" t="s">
         <v>31</v>
       </c>
+      <c r="L4" s="10" t="s">
+        <v>32</v>
+      </c>
       <c r="M4" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="N4" s="9" t="s">
         <v>33</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="O4" s="10" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -808,10 +1046,10 @@
         <v>10101</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>37</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>10101</v>
@@ -820,105 +1058,287 @@
         <v>5</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="H5" s="1" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="I5" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="n">
         <v>10102</v>
       </c>
-      <c r="J5" s="1" t="n">
-        <v>10103</v>
-      </c>
-      <c r="K5" s="1" t="n">
-        <v>3900</v>
-      </c>
-      <c r="L5" s="1" t="n">
-        <v>390</v>
-      </c>
-      <c r="M5" s="1" t="n">
-        <v>3</v>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="0"/>
-      <c r="B6" s="0" t="n">
-        <v>10102</v>
-      </c>
-      <c r="C6" s="0"/>
-      <c r="D6" s="0"/>
-      <c r="E6" s="0"/>
-      <c r="F6" s="0"/>
-      <c r="G6" s="0"/>
-      <c r="H6" s="0"/>
-      <c r="I6" s="0"/>
-      <c r="J6" s="0"/>
-      <c r="K6" s="0"/>
-      <c r="L6" s="0"/>
-      <c r="M6" s="0"/>
-      <c r="N6" s="0"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="2" t="n">
+        <v>10101</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G6" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="n">
         <v>10103</v>
       </c>
+      <c r="E7" s="2" t="n">
+        <v>10101</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="n">
         <v>10104</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="49.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="E8" s="2" t="n">
+        <v>10101</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="n">
-        <v>201</v>
+        <v>20101</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>10101</v>
       </c>
       <c r="F9" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="n">
+        <v>100101</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>100101</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="0" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="1" t="n">
+    </row>
+    <row r="11" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="n">
+        <v>30101</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>30101</v>
+      </c>
+      <c r="F11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="G11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I9" s="1" t="n">
-        <v>20102</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>20103</v>
-      </c>
-      <c r="K9" s="1" t="n">
-        <v>5000</v>
-      </c>
-      <c r="L9" s="1" t="n">
-        <v>500</v>
-      </c>
-      <c r="M9" s="1" t="n">
+      <c r="I11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="N9" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="XFB9" s="0"/>
-      <c r="XFC9" s="0"/>
-      <c r="XFD9" s="0"/>
+      <c r="K11" s="1" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="L11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="n">
+        <v>40101</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>40101</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="L12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="n">
+        <v>40102</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>40102</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="I22" s="1" t="s">
-        <v>39</v>
+      <c r="H22" s="1" t="s">
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -937,9 +1357,567 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1"/>
+  <dimension ref="A1:O22"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="28.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="22.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="22.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="16.42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="22.12"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>53</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="6"/>
+      <c r="C3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="88.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="13" t="s">
+        <v>60</v>
+      </c>
+      <c r="F4" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="G4" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="O4" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="n">
+        <v>10101</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>71</v>
+      </c>
+      <c r="D5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="H5" s="0" t="n">
+        <v>300</v>
+      </c>
+      <c r="I5" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="n">
+        <v>10102</v>
+      </c>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="n">
+        <v>10103</v>
+      </c>
+      <c r="D7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="n">
+        <v>10104</v>
+      </c>
+      <c r="D8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="n">
+        <v>20101</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="H9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="n">
+        <v>100101</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="H10" s="0" t="n">
+        <v>820</v>
+      </c>
+      <c r="I10" s="0" t="n">
+        <v>82</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="n">
+        <v>30101</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="n">
+        <v>40101</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="H12" s="0" t="n">
+        <v>360</v>
+      </c>
+      <c r="I12" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="n">
+        <v>40102</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="D13" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="H13" s="0" t="n">
+        <v>320</v>
+      </c>
+      <c r="I13" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="J13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="K13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="0" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="N22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="O22" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlSkill.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlSkill.xlsx
@@ -5,11 +5,11 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="BrawlSkill" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="BrawProjectile" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="BrawlProjectile" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="93">
   <si>
     <t xml:space="preserve">##var</t>
   </si>
@@ -35,13 +35,31 @@
     <t xml:space="preserve">Description</t>
   </si>
   <si>
-    <t xml:space="preserve">ProjectileID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ProjectileCount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDTime</t>
+    <t xml:space="preserve">ProjectileId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProjectilesPerVolley </t>
+  </si>
+  <si>
+    <t xml:space="preserve">EmitterType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EmitterParam1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EmitterParam2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EmitterParam3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AmmoCapacity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ReloadTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CooldownTime</t>
   </si>
   <si>
     <t xml:space="preserve">SkillType</t>
@@ -51,91 +69,99 @@
   </si>
   <si>
     <t xml:space="preserve">SkillRangeParam1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkillRangeParam2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkillCastRangeType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkillCastParam1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkillCastParam2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">float</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##</t>
+  </si>
+  <si>
+    <t xml:space="preserve">技能 ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">名字</t>
+  </si>
+  <si>
+    <t xml:space="preserve">描述</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t xml:space="preserve">每一轮子弹数量</t>
   </si>
   <si>
     <r>
       <rPr>
-        <b val="true"/>
         <sz val="10"/>
         <color rgb="FF222222"/>
         <rFont val="Microsoft YaHei"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Skill</t>
+      <t xml:space="preserve">技能发射器类型
+</t>
     </r>
     <r>
       <rPr>
-        <b val="true"/>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">Range</t>
-    </r>
-    <r>
-      <rPr>
-        <b val="true"/>
-        <sz val="10"/>
+        <sz val="11"/>
         <color rgb="FF222222"/>
         <rFont val="Microsoft YaHei"/>
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">Param2</t>
+      <t xml:space="preserve">1 霰弹枪发射器
+2 左轮手枪发射器
+3 近战小刀发射器
+4 回旋镖发射器
+5 预留</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">SkillCastRangeType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SkillCastParam1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SkillCastParam2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SkillEmmiterType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">##type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">int</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string</t>
-  </si>
-  <si>
-    <t xml:space="preserve">float</t>
-  </si>
-  <si>
-    <t xml:space="preserve">##group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">c</t>
-  </si>
-  <si>
-    <t xml:space="preserve">##</t>
-  </si>
-  <si>
-    <t xml:space="preserve">技能 ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">名字</t>
-  </si>
-  <si>
-    <t xml:space="preserve">描述</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  抛射体   ID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">子弹数量</t>
+    <t xml:space="preserve">技能发射器参数1（通常是发射次数，所以这里是int比较好，不同发射器的解释也不一样，后续可以修改为float）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">技能发射器参数2（通常是发射间隔）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">技能发射器参数3（通常是子弹发射间隔）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">装弹数量</t>
   </si>
   <si>
     <t xml:space="preserve">装弹时间</t>
+  </si>
+  <si>
+    <t xml:space="preserve">冷却时间</t>
   </si>
   <si>
     <t xml:space="preserve">技能类型
@@ -161,6 +187,7 @@
         <color rgb="FF222222"/>
         <rFont val="Microsoft YaHei"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> 
 </t>
@@ -182,35 +209,7 @@
     <t xml:space="preserve">技能范围参数1</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">技能</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-      </rPr>
-      <t xml:space="preserve">范围</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF222222"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">参数2，有参数1的时候，参数2才有效</t>
-    </r>
+    <t xml:space="preserve">技能范围参数2，有参数1的时候，参数2才有效</t>
   </si>
   <si>
     <r>
@@ -230,6 +229,7 @@
         <color rgb="FF222222"/>
         <rFont val="Microsoft YaHei"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">SkillRangeType
 </t>
@@ -243,20 +243,19 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1 矩形
-2 扇形
-3 圆形</t>
+2 抛物线
+3 预留</t>
     </r>
   </si>
   <si>
     <t xml:space="preserve">技能施放参数1
-等于0 没有距离，原地释放
-大于0 有抛物线/矩形等 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">技能施放参数2，有参数1的时候，参数2才有效</t>
-  </si>
-  <si>
-    <t xml:space="preserve">技能发射器类型</t>
+矩形是长度
+抛物线是最小长度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">技能施放参数2，有参数1的时候，参数2才有效
+矩形是宽度
+抛物线是最大长度</t>
   </si>
   <si>
     <t xml:space="preserve">大口径霰弹枪</t>
@@ -268,7 +267,7 @@
     <t xml:space="preserve">公牛普通攻击</t>
   </si>
   <si>
-    <t xml:space="preserve">连续发射2次</t>
+    <t xml:space="preserve">连续发射2次霰弹枪</t>
   </si>
   <si>
     <t xml:space="preserve">卡尔普通攻击</t>
@@ -295,16 +294,19 @@
     <t xml:space="preserve">柯尔特迅速开火，射出大量子弹，这些子弹的射程更远且能摧毁掩体。</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Target</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CollisionDestroyedCount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Duration</t>
+    <t xml:space="preserve">Radius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlockMask </t>
+  </si>
+  <si>
+    <t xml:space="preserve">TargetMask</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHitCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lifetime</t>
   </si>
   <si>
     <t xml:space="preserve">Speed</t>
@@ -316,16 +318,28 @@
     <t xml:space="preserve">ValueGrowthPerLevel</t>
   </si>
   <si>
-    <t xml:space="preserve">CollisionEvent1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CollisionEventParam1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CollisionEventParam2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CollisionEvent2</t>
+    <t xml:space="preserve">HitEvent1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HitEvent1Param1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HitEvent1Param2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HitEvent2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HitEvent2Param1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HitEvent2Param2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  抛射体   ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">碰撞半径（现在默认子弹都是球体方便计算）</t>
   </si>
   <si>
     <r>
@@ -335,8 +349,9 @@
         <color rgb="FF222222"/>
         <rFont val="Microsoft YaHei"/>
         <family val="0"/>
+        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">有效目标
+      <t xml:space="preserve">可被阻挡的目标
 </t>
     </r>
     <r>
@@ -345,6 +360,36 @@
         <color rgb="FF222222"/>
         <rFont val="Microsoft YaHei"/>
         <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">0 无
+1 不可摧毁墙
+2 可摧毁墙体
+4 敌方
+8 友方
+16 可摧毁草</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">生效目标
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">0 无
 1 敌方
@@ -354,7 +399,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">耐久度，即碰撞几次再销毁，一般需要碰到有效目标才算</t>
+    <t xml:space="preserve">耐久度，即生效几次再销毁，一般需要碰到有效目标才算</t>
   </si>
   <si>
     <t xml:space="preserve">持续时间</t>
@@ -369,28 +414,31 @@
     <t xml:space="preserve">额外数值</t>
   </si>
   <si>
-    <t xml:space="preserve">碰撞事件1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">碰撞事件1参数1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">碰撞事件1参数2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">碰撞事件2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">碰撞事件2参数1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">碰撞事件2参数2</t>
+    <t xml:space="preserve">击中事件1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">击中事件1参数1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">击中事件1参数2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">击中事件2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">击中事件2参数1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">击中事件2参数2</t>
   </si>
   <si>
     <t xml:space="preserve">雪莉的霰弹枪的子弹</t>
   </si>
   <si>
-    <t xml:space="preserve">卡尔丢出的回旋镖</t>
+    <t xml:space="preserve">连续发射2次</t>
+  </si>
+  <si>
+    <t xml:space="preserve">卡尔丢出的回旋镖（回弹时不受阻挡影响）</t>
   </si>
   <si>
     <t xml:space="preserve">武士的小刀效果</t>
@@ -409,7 +457,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="13">
+  <fonts count="9">
     <font>
       <sz val="10"/>
       <name val="Noto Sans SC"/>
@@ -454,13 +502,6 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="10"/>
-      <color rgb="FF222222"/>
-      <name val="Microsoft YaHei"/>
-      <family val="0"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF222222"/>
       <name val="Microsoft YaHei"/>
@@ -473,25 +514,6 @@
       <name val="Microsoft YaHei"/>
       <family val="0"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF222222"/>
-      <name val="Microsoft YaHei"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF222222"/>
-      <name val="Microsoft YaHei"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF222222"/>
-      <name val="Microsoft YaHei"/>
-      <family val="0"/>
     </font>
   </fonts>
   <fills count="5">
@@ -558,7 +580,7 @@
       <protection locked="true" hidden="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -583,23 +605,23 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -607,11 +629,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -862,19 +880,21 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.54"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="2" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="16.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="14.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="8" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="21"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="13" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16383" min="16379" style="0" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="1" width="23.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="19.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="14" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="19" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -902,7 +922,7 @@
       <c r="H1" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="5" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="5" t="s">
@@ -920,67 +940,97 @@
       <c r="N1" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="3" t="s">
         <v>14</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>16</v>
+        <v>21</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="S2" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="T2" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="6" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E3" s="7"/>
       <c r="F3" s="6"/>
@@ -993,52 +1043,72 @@
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
     </row>
     <row r="4" customFormat="false" ht="121.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>27</v>
+        <v>31</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>32</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="L4" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="M4" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="N4" s="10" t="s">
+      <c r="I4" s="9" t="s">
         <v>34</v>
       </c>
+      <c r="J4" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L4" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="N4" s="9" t="s">
+        <v>39</v>
+      </c>
       <c r="O4" s="10" t="s">
-        <v>35</v>
+        <v>40</v>
+      </c>
+      <c r="P4" s="10" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q4" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="R4" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="S4" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="T4" s="10" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1046,10 +1116,10 @@
         <v>10101</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>10101</v>
@@ -1058,31 +1128,46 @@
         <v>5</v>
       </c>
       <c r="G5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="H5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1" t="n">
+      <c r="M5" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="P5" s="1" t="n">
         <v>7.67</v>
       </c>
-      <c r="K5" s="1" t="n">
+      <c r="Q5" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="L5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="1" t="n">
-        <v>1</v>
+      <c r="R5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1096,10 +1181,13 @@
       <c r="F6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="1" t="n">
+      <c r="L6" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="H6" s="1" t="n">
+      <c r="M6" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N6" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1113,10 +1201,13 @@
       <c r="F7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="G7" s="1" t="n">
+      <c r="L7" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="H7" s="1" t="n">
+      <c r="M7" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N7" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1130,10 +1221,13 @@
       <c r="F8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="G8" s="1" t="n">
+      <c r="L8" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="H8" s="1" t="n">
+      <c r="M8" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N8" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1142,10 +1236,10 @@
         <v>20101</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>10101</v>
@@ -1154,9 +1248,27 @@
         <v>5</v>
       </c>
       <c r="G9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L9" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="H9" s="1" t="n">
+      <c r="M9" s="1" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N9" s="1" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1165,10 +1277,10 @@
         <v>100101</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>100101</v>
@@ -1177,31 +1289,37 @@
         <v>1</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J10" s="1" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K10" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="0" t="n">
-        <v>1</v>
+        <v>1</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>0</v>
       </c>
       <c r="M10" s="1" t="n">
         <v>0</v>
       </c>
       <c r="N10" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10" s="1" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1209,10 +1327,10 @@
         <v>30101</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>30101</v>
@@ -1221,31 +1339,46 @@
         <v>2</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J11" s="1" t="n">
+      <c r="O11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="K11" s="1" t="n">
+      <c r="Q11" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="L11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="1" t="n">
-        <v>3</v>
+      <c r="R11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1253,10 +1386,10 @@
         <v>40101</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>40101</v>
@@ -1265,31 +1398,46 @@
         <v>6</v>
       </c>
       <c r="G12" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K12" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="L12" s="1" t="n">
         <v>1.6</v>
       </c>
-      <c r="H12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="1" t="n">
+      <c r="M12" s="1" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="K12" s="1" t="n">
+      <c r="Q12" s="1" t="n">
         <v>0.7</v>
       </c>
-      <c r="L12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="1" t="n">
-        <v>4</v>
+      <c r="R12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1297,10 +1445,10 @@
         <v>40102</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>40102</v>
@@ -1309,36 +1457,46 @@
         <v>12</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" s="1" t="n">
         <v>1</v>
       </c>
       <c r="I13" s="1" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" s="1" t="n">
+        <v>0.08333</v>
+      </c>
+      <c r="K13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="K13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="L13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="1" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H22" s="1" t="s">
-        <v>48</v>
+      <c r="Q13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1357,21 +1515,22 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:Q13"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="2" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="28.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="6" style="1" width="23.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="22.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="16.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="23.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="22.12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="16.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="23.23"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="22.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="2" width="16.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="16.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="28.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="1" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="22.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="22.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="22.12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1384,99 +1543,111 @@
       <c r="C1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="5" t="s">
-        <v>49</v>
+      <c r="D1" s="4" t="s">
+        <v>58</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>50</v>
+        <v>59</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="G1" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="H1" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="I1" s="12" t="s">
-        <v>54</v>
+        <v>61</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>63</v>
       </c>
       <c r="J1" s="5" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="L1" s="5" t="s">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="M1" s="5" t="s">
-        <v>58</v>
+        <v>67</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>57</v>
+        <v>69</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>16</v>
+        <v>22</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>23</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G2" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="J2" s="6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L2" s="6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="M2" s="6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="N2" s="6" t="s">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="O2" s="6" t="s">
-        <v>16</v>
+        <v>21</v>
+      </c>
+      <c r="P2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="B3" s="6"/>
       <c r="C3" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="D3" s="6"/>
+        <v>25</v>
+      </c>
+      <c r="D3" s="7"/>
       <c r="E3" s="6"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
@@ -1488,52 +1659,60 @@
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
       <c r="O3" s="6"/>
-    </row>
-    <row r="4" customFormat="false" ht="88.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="103.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>25</v>
+        <v>72</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="F4" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="H4" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="J4" s="9" t="s">
-        <v>65</v>
+        <v>29</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="E4" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="H4" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="I4" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="J4" s="12" t="s">
+        <v>79</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>66</v>
+        <v>80</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>68</v>
+        <v>82</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>69</v>
+        <v>83</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>70</v>
+        <v>84</v>
+      </c>
+      <c r="P4" s="9" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q4" s="9" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1541,42 +1720,48 @@
         <v>10101</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>71</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>1</v>
+        <v>87</v>
+      </c>
+      <c r="D5" s="11" t="n">
+        <v>0.05</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H5" s="0" t="n">
+      <c r="J5" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="I5" s="0" t="n">
+      <c r="K5" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="J5" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O5" s="0" t="n">
+      <c r="L5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1585,31 +1770,32 @@
         <v>10102</v>
       </c>
       <c r="C6" s="1"/>
-      <c r="D6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="0" t="n">
-        <v>0</v>
+      <c r="D6" s="11"/>
+      <c r="F6" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="J6" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O6" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1617,31 +1803,32 @@
       <c r="B7" s="1" t="n">
         <v>10103</v>
       </c>
-      <c r="D7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="0" t="n">
-        <v>0</v>
+      <c r="D7" s="11"/>
+      <c r="F7" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="J7" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O7" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1649,31 +1836,32 @@
       <c r="B8" s="1" t="n">
         <v>10104</v>
       </c>
-      <c r="D8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="0" t="n">
-        <v>0</v>
+      <c r="D8" s="11"/>
+      <c r="F8" s="1" t="n">
+        <v>1</v>
       </c>
       <c r="J8" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1682,86 +1870,98 @@
         <v>20101</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>1</v>
+        <v>88</v>
+      </c>
+      <c r="D9" s="11" t="n">
+        <v>0.05</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="H9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="0" t="n">
-        <v>0</v>
-      </c>
       <c r="J9" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="1" t="n">
         <v>100101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D10" s="1" t="n">
+        <v>89</v>
+      </c>
+      <c r="D10" s="2" t="n">
         <v>1</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="H10" s="0" t="n">
+      <c r="J10" s="1" t="n">
         <v>820</v>
       </c>
-      <c r="I10" s="0" t="n">
+      <c r="K10" s="1" t="n">
         <v>82</v>
       </c>
-      <c r="J10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="0" t="n">
+      <c r="L10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1770,10 +1970,10 @@
         <v>30101</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>1</v>
+        <v>90</v>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.3</v>
       </c>
       <c r="E11" s="1" t="n">
         <v>0</v>
@@ -1784,28 +1984,34 @@
       <c r="G11" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="H11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="0" t="n">
+      <c r="H11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="n">
         <v>0</v>
       </c>
       <c r="J11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="0" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1814,42 +2020,48 @@
         <v>40101</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>1</v>
+        <v>91</v>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.04</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H12" s="0" t="n">
+      <c r="J12" s="1" t="n">
         <v>360</v>
       </c>
-      <c r="I12" s="0" t="n">
+      <c r="K12" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="J12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="0" t="n">
+      <c r="L12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1858,63 +2070,49 @@
         <v>40102</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D13" s="1" t="n">
+        <v>92</v>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="F13" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="E13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>0</v>
-      </c>
       <c r="G13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="H13" s="0" t="n">
+      <c r="J13" s="1" t="n">
         <v>320</v>
       </c>
-      <c r="I13" s="0" t="n">
+      <c r="K13" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="J13" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="K13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="0" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="0" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="H22" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="N22" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="O22" s="1" t="s">
-        <v>48</v>
+      <c r="L13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlSkill.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlSkill.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="BrawlSkill" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="95">
   <si>
     <t xml:space="preserve">##var</t>
   </si>
@@ -336,6 +336,9 @@
     <t xml:space="preserve">HitEvent2Param2</t>
   </si>
   <si>
+    <t xml:space="preserve">SuperChargeOnHit</t>
+  </si>
+  <si>
     <t xml:space="preserve">  抛射体   ID</t>
   </si>
   <si>
@@ -430,6 +433,9 @@
   </si>
   <si>
     <t xml:space="preserve">击中事件2参数2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每枚弹丸对有效目标实际扣血后获得的大招格数；0不充能，与技能类型无关</t>
   </si>
   <si>
     <t xml:space="preserve">雪莉的霰弹枪的子弹</t>
@@ -1181,6 +1187,9 @@
       <c r="F6" s="1" t="n">
         <v>5</v>
       </c>
+      <c r="K6" s="1" t="n">
+        <v>1</v>
+      </c>
       <c r="L6" s="1" t="n">
         <v>1.5</v>
       </c>
@@ -1515,7 +1524,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
@@ -1585,6 +1594,9 @@
       <c r="Q1" s="5" t="s">
         <v>71</v>
       </c>
+      <c r="R1" s="5" t="s">
+        <v>72</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
@@ -1637,6 +1649,9 @@
       </c>
       <c r="Q2" s="6" t="s">
         <v>21</v>
+      </c>
+      <c r="R2" s="6" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1661,58 +1676,62 @@
       <c r="O3" s="6"/>
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
-    </row>
-    <row r="4" customFormat="false" ht="103.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="R3" s="6"/>
+    </row>
+    <row r="4" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
         <v>26</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>29</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E4" s="12" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F4" s="12" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G4" s="12" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H4" s="12" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I4" s="12" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J4" s="12" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K4" s="9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L4" s="9" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M4" s="9" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N4" s="9" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="O4" s="9" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="P4" s="9" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="Q4" s="9" t="s">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R4" s="9" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1720,7 +1739,7 @@
         <v>10101</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="D5" s="11" t="n">
         <v>0.05</v>
@@ -1763,6 +1782,9 @@
       </c>
       <c r="Q5" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1798,6 +1820,9 @@
       <c r="Q6" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="R6" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="1" t="n">
@@ -1831,6 +1856,9 @@
       <c r="Q7" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="R7" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="1" t="n">
@@ -1864,13 +1892,16 @@
       <c r="Q8" s="1" t="n">
         <v>0</v>
       </c>
+      <c r="R8" s="1" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="1" t="n">
         <v>20101</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="D9" s="11" t="n">
         <v>0.05</v>
@@ -1912,6 +1943,9 @@
         <v>0</v>
       </c>
       <c r="Q9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1920,7 +1954,7 @@
         <v>100101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>1</v>
@@ -1962,6 +1996,9 @@
         <v>0</v>
       </c>
       <c r="Q10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1970,7 +2007,7 @@
         <v>30101</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>0.3</v>
@@ -2012,6 +2049,9 @@
         <v>0</v>
       </c>
       <c r="Q11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2020,7 +2060,7 @@
         <v>40101</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>0.04</v>
@@ -2063,6 +2103,9 @@
       </c>
       <c r="Q12" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2070,7 +2113,7 @@
         <v>40102</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>0.06</v>
@@ -2113,6 +2156,9 @@
       </c>
       <c r="Q13" s="1" t="n">
         <v>0</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>0.1</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlSkill.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlSkill.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="BrawlSkill" sheetId="1" state="visible" r:id="rId3"/>
@@ -13,7 +13,7 @@
     <sheet name="BrawlCollisionRule" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="碰撞配置说明" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001" fullCalcOnLoad="1" fullPrecision="1"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -23,140 +23,147 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>Id</t>
-  </si>
-  <si>
-    <t>Name</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>ProjectileId</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="197">
+  <si>
+    <t xml:space="preserve">##var</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Description</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ProjectileId</t>
   </si>
   <si>
     <t xml:space="preserve">ProjectilesPerVolley </t>
   </si>
   <si>
-    <t>EmitterType</t>
-  </si>
-  <si>
-    <t>EmitterParam1</t>
-  </si>
-  <si>
-    <t>EmitterParam2</t>
-  </si>
-  <si>
-    <t>EmitterParam3</t>
-  </si>
-  <si>
-    <t>AmmoCapacity</t>
-  </si>
-  <si>
-    <t>ReloadTime</t>
-  </si>
-  <si>
-    <t>CooldownTime</t>
-  </si>
-  <si>
-    <t>SkillType</t>
-  </si>
-  <si>
-    <t>SkillRangeType</t>
-  </si>
-  <si>
-    <t>SkillRangeParam1</t>
-  </si>
-  <si>
-    <t>SkillRangeParam2</t>
-  </si>
-  <si>
-    <t>SkillCastRangeType</t>
-  </si>
-  <si>
-    <t>SkillCastParam1</t>
-  </si>
-  <si>
-    <t>SkillCastParam2</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>##group</t>
-  </si>
-  <si>
-    <t>c</t>
-  </si>
-  <si>
-    <t>##</t>
-  </si>
-  <si>
-    <t>技能 ID</t>
-  </si>
-  <si>
-    <t>名字</t>
-  </si>
-  <si>
-    <t>描述</t>
+    <t xml:space="preserve">EmitterType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EmitterParam1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EmitterParam2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EmitterParam3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AmmoCapacity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ReloadTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CooldownTime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkillType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkillRangeType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkillRangeParam1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkillRangeParam2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkillCastRangeType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkillCastParam1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SkillCastParam2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string</t>
+  </si>
+  <si>
+    <t xml:space="preserve">float</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">c</t>
+  </si>
+  <si>
+    <t xml:space="preserve">##</t>
+  </si>
+  <si>
+    <t xml:space="preserve">技能 ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">名字</t>
+  </si>
+  <si>
+    <t xml:space="preserve">描述</t>
   </si>
   <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t>每一轮子弹数量</t>
+    <t xml:space="preserve">每一轮子弹数量</t>
   </si>
   <si>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
         <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
         <charset val="1"/>
-        <color rgb="FF222222"/>
-        <sz val="10"/>
       </rPr>
-      <t xml:space="preserve">技能发射器类型_x000A_</t>
+      <t xml:space="preserve">技能发射器类型
+</t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
         <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
         <charset val="1"/>
-        <color rgb="FF222222"/>
-        <sz val="11"/>
       </rPr>
-      <t>1 霰弹枪发射器_x000A_2 左轮手枪发射器_x000A_3 近战小刀发射器_x000A_4 回旋镖发射器_x000A_5 预留</t>
+      <t xml:space="preserve">1 霰弹枪发射器
+2 左轮手枪发射器
+3 近战小刀发射器
+4 回旋镖发射器
+5 预留</t>
     </r>
   </si>
   <si>
-    <t>技能发射器参数1（通常是发射次数，所以这里是int比较好，不同发射器的解释也不一样，后续可以修改为float）</t>
-  </si>
-  <si>
-    <t>技能发射器参数2（通常是发射间隔）</t>
-  </si>
-  <si>
-    <t>技能发射器参数3（通常是子弹发射间隔）</t>
-  </si>
-  <si>
-    <t>装弹数量</t>
-  </si>
-  <si>
-    <t>装弹时间</t>
-  </si>
-  <si>
-    <t>冷却时间</t>
+    <t xml:space="preserve">技能发射器参数1（通常是发射次数，所以这里是int比较好，不同发射器的解释也不一样，后续可以修改为float）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">技能发射器参数2（通常是发射间隔）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">技能发射器参数3（通常是子弹发射间隔）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">装弹数量</t>
+  </si>
+  <si>
+    <t xml:space="preserve">装弹时间</t>
+  </si>
+  <si>
+    <t xml:space="preserve">冷却时间</t>
   </si>
   <si>
     <t xml:space="preserve">技能类型
@@ -168,66 +175,78 @@
   <si>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
         <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
         <charset val="1"/>
-        <color rgb="FF222222"/>
-        <sz val="10"/>
       </rPr>
       <t xml:space="preserve">技能范围类型 </t>
     </r>
     <r>
       <rPr>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
         <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
         <charset val="1"/>
-        <color rgb="FF222222"/>
-        <sz val="11"/>
       </rPr>
-      <t xml:space="preserve"> _x000A_</t>
+      <t xml:space="preserve"> 
+</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
         <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
         <charset val="1"/>
-        <color rgb="FF222222"/>
-        <sz val="10"/>
       </rPr>
-      <t>1 矩形_x000A_2 扇形_x000A_3 圆形</t>
+      <t xml:space="preserve">1 矩形
+2 扇形
+3 圆形</t>
     </r>
   </si>
   <si>
-    <t>技能范围参数1</t>
-  </si>
-  <si>
-    <t>技能范围参数2，有参数1的时候，参数2才有效</t>
+    <t xml:space="preserve">技能范围参数1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">技能范围参数2，有参数1的时候，参数2才有效</t>
   </si>
   <si>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
         <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
         <charset val="1"/>
-        <color rgb="FF222222"/>
-        <sz val="10"/>
       </rPr>
-      <t>技能施放范围类型等于0就用</t>
+      <t xml:space="preserve">技能施放范围类型等于0就用</t>
     </r>
     <r>
       <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF222222"/>
         <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
         <charset val="1"/>
-        <b/>
-        <color rgb="FF222222"/>
-        <sz val="11"/>
       </rPr>
-      <t xml:space="preserve">SkillRangeType_x000A_</t>
+      <t xml:space="preserve">SkillRangeType
+</t>
     </r>
     <r>
       <rPr>
+        <sz val="10"/>
+        <color rgb="FF222222"/>
         <rFont val="Microsoft YaHei"/>
+        <family val="0"/>
         <charset val="1"/>
-        <color rgb="FF222222"/>
-        <sz val="10"/>
       </rPr>
-      <t>1 矩形_x000A_2 抛物线_x000A_3 预留</t>
+      <t xml:space="preserve">1 矩形
+2 抛物线
+3 预留</t>
     </r>
   </si>
   <si>
@@ -241,473 +260,482 @@
 抛物线是最大长度</t>
   </si>
   <si>
-    <t>大口径霰弹枪</t>
-  </si>
-  <si>
-    <t>雪莉的霰弹枪可大范围射出多枚射程较远的弹丸，命中敌人的弹丸越多，造成的伤害越高。</t>
-  </si>
-  <si>
-    <t>超级霰弹</t>
-  </si>
-  <si>
-    <t>雪莉的超级霰弹可摧毁掩体直击对手。被命中的敌人即时未被击倒也会被击退。</t>
-  </si>
-  <si>
-    <t>公牛普通攻击</t>
-  </si>
-  <si>
-    <t>连续发射2次霰弹枪</t>
-  </si>
-  <si>
-    <t>卡尔普通攻击</t>
-  </si>
-  <si>
-    <t>卡尔丢出回旋镖</t>
-  </si>
-  <si>
-    <t>武士普通攻击</t>
-  </si>
-  <si>
-    <t>用小刀捅2下.且发出强劲的刀风。</t>
-  </si>
-  <si>
-    <t>左轮手枪</t>
-  </si>
-  <si>
-    <t>柯尔特使用它的左轮手枪向同一方向连开6枪，可攻击到远距离的的人。</t>
-  </si>
-  <si>
-    <t>子弹风暴</t>
-  </si>
-  <si>
-    <t>柯尔特迅速开火，射出大量子弹，这些子弹的射程更远且能摧毁掩体。</t>
-  </si>
-  <si>
-    <t>ModelPath</t>
-  </si>
-  <si>
-    <t>ImpactEffectPath</t>
-  </si>
-  <si>
-    <t>ExpireEffectPath</t>
-  </si>
-  <si>
-    <t>Radius</t>
-  </si>
-  <si>
-    <t>MaxHitCount</t>
-  </si>
-  <si>
-    <t>Lifetime</t>
-  </si>
-  <si>
-    <t>Speed</t>
-  </si>
-  <si>
-    <t>Value</t>
-  </si>
-  <si>
-    <t>ValueGrowthPerLevel</t>
-  </si>
-  <si>
-    <t>HitEvent1</t>
-  </si>
-  <si>
-    <t>HitEvent1Param1</t>
-  </si>
-  <si>
-    <t>HitEvent1Param2</t>
-  </si>
-  <si>
-    <t>HitEvent2</t>
-  </si>
-  <si>
-    <t>HitEvent2Param1</t>
-  </si>
-  <si>
-    <t>HitEvent2Param2</t>
-  </si>
-  <si>
-    <t>SuperChargeOnHit</t>
-  </si>
-  <si>
-    <t>CollisionRuleGroupId</t>
+    <t xml:space="preserve">大口径霰弹枪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雪莉的霰弹枪可大范围射出多枚射程较远的弹丸，命中敌人的弹丸越多，造成的伤害越高。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">超级霰弹</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雪莉的超级霰弹可摧毁掩体直击对手。被命中的敌人即时未被击倒也会被击退。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">公牛普通攻击</t>
+  </si>
+  <si>
+    <t xml:space="preserve">连续发射2次霰弹枪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">卡尔普通攻击</t>
+  </si>
+  <si>
+    <t xml:space="preserve">卡尔丢出回旋镖</t>
+  </si>
+  <si>
+    <t xml:space="preserve">武士普通攻击</t>
+  </si>
+  <si>
+    <t xml:space="preserve">用小刀捅2下.且发出强劲的刀风。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">左轮手枪</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柯尔特使用它的左轮手枪向同一方向连开6枪，可攻击到远距离的的人。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">子弹风暴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柯尔特迅速开火，射出大量子弹，这些子弹的射程更远且能摧毁掩体。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ModelPath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ImpactEffectPath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExpireEffectPath</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Radius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MaxHitCount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lifetime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Speed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ValueGrowthPerLevel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HitEvent1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HitEvent1Param1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HitEvent1Param2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HitEvent2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HitEvent2Param1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HitEvent2Param2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperChargeOnHit</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CollisionRuleGroupId</t>
   </si>
   <si>
     <t xml:space="preserve">  抛射体   ID</t>
   </si>
   <si>
-    <t>模型路径</t>
-  </si>
-  <si>
-    <t>碰撞到有效目标或阻挡物时的特效</t>
-  </si>
-  <si>
-    <t>到达射程终点、寿命结束时的特效</t>
-  </si>
-  <si>
-    <t>碰撞半径（现在默认子弹都是球体方便计算）</t>
-  </si>
-  <si>
-    <t>耐久度，即生效几次再销毁，一般需要碰到有效目标才算</t>
-  </si>
-  <si>
-    <t>持续时间</t>
-  </si>
-  <si>
-    <t>速度</t>
-  </si>
-  <si>
-    <t>基础数值</t>
-  </si>
-  <si>
-    <t>额外数值</t>
-  </si>
-  <si>
-    <t>击中事件1</t>
-  </si>
-  <si>
-    <t>击中事件1参数1</t>
-  </si>
-  <si>
-    <t>击中事件1参数2</t>
-  </si>
-  <si>
-    <t>击中事件2</t>
-  </si>
-  <si>
-    <t>击中事件2参数1</t>
-  </si>
-  <si>
-    <t>击中事件2参数2</t>
-  </si>
-  <si>
-    <t>每枚弹丸对有效目标实际扣血后获得的大招格数；0不充能，与技能类型无关</t>
-  </si>
-  <si>
-    <t>碰撞规则组ID，引用BrawlCollisionRule.GroupId。1=墙阻挡/敌方作战单位生效并阻挡；2=不可摧毁墙阻挡/可摧毁场景物和敌方作战单位生效并穿透。仅源表设计，待代码接入。</t>
-  </si>
-  <si>
-    <t>雪莉的霰弹枪的子弹</t>
-  </si>
-  <si>
-    <t>Projectile 10</t>
-  </si>
-  <si>
-    <t>Hit 10</t>
-  </si>
-  <si>
-    <t>Flash 10</t>
-  </si>
-  <si>
-    <t>雪莉的霰弹枪的大招子弹</t>
-  </si>
-  <si>
-    <t>Projectile 6</t>
-  </si>
-  <si>
-    <t>Hit 6</t>
-  </si>
-  <si>
-    <t>Flash 6</t>
-  </si>
-  <si>
-    <t>连续发射2次</t>
-  </si>
-  <si>
-    <t>卡尔丢出的回旋镖（回弹时不受阻挡影响）</t>
-  </si>
-  <si>
-    <t>武士的小刀效果</t>
-  </si>
-  <si>
-    <t>柯尔特的手枪子弹</t>
-  </si>
-  <si>
-    <t>Projectile 1</t>
-  </si>
-  <si>
-    <t>Hit 1</t>
-  </si>
-  <si>
-    <t>Flash 1</t>
-  </si>
-  <si>
-    <t>柯尔特的大招子弹</t>
-  </si>
-  <si>
-    <t>Projectile 14</t>
-  </si>
-  <si>
-    <t>Hit 14</t>
-  </si>
-  <si>
-    <t>Flash 14</t>
-  </si>
-  <si>
-    <t>GroupId</t>
-  </si>
-  <si>
-    <t>RequiredLayerMask</t>
-  </si>
-  <si>
-    <t>ExcludedLayerMask</t>
-  </si>
-  <si>
-    <t>RelationMask</t>
-  </si>
-  <si>
-    <t>BlockProjectile</t>
-  </si>
-  <si>
-    <t>ApplyHitEvents</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>规则行ID</t>
-  </si>
-  <si>
-    <t>规则组ID；同组多行取或</t>
-  </si>
-  <si>
-    <t>规则说明</t>
-  </si>
-  <si>
-    <t>必须同时具备全部位；0不限</t>
-  </si>
-  <si>
-    <t>不能具有任意一位；0不排除</t>
-  </si>
-  <si>
-    <t>1敌对；2友善/同阵营；3不限；0不匹配</t>
-  </si>
-  <si>
-    <t>匹配后终止弹丸飞行</t>
-  </si>
-  <si>
-    <t>匹配后执行弹丸HitEvent组；同次接触仅执行一次</t>
-  </si>
-  <si>
-    <t>普攻：所有墙体只阻挡</t>
-  </si>
-  <si>
-    <t>普攻：敌方作战单位生效并阻挡</t>
-  </si>
-  <si>
-    <t>穿透大招：不可摧毁墙只阻挡</t>
-  </si>
-  <si>
-    <t>穿透大招：可摧毁墙生效并穿透</t>
-  </si>
-  <si>
-    <t>穿透大招：敌方作战单位生效并穿透</t>
-  </si>
-  <si>
-    <t>穿透大招：可摧毁草生效并穿透</t>
-  </si>
-  <si>
-    <t>项目</t>
-  </si>
-  <si>
-    <t>值或规则</t>
-  </si>
-  <si>
-    <t>说明</t>
-  </si>
-  <si>
-    <t>实施状态</t>
-  </si>
-  <si>
-    <t>仅源表设计，未导出、未接入代码</t>
-  </si>
-  <si>
-    <t>当前游戏仍使用旧生成配置；后续需同步代码和Luban表注册再导出。</t>
-  </si>
-  <si>
-    <t>Hero</t>
-  </si>
-  <si>
-    <t>英雄标签；英雄组合Hero|Battle=5。英雄表本次不改。</t>
-  </si>
-  <si>
-    <t>Monster</t>
-  </si>
-  <si>
-    <t>怪物标签；劫匪组合Monster|Battle=6。</t>
-  </si>
-  <si>
-    <t>Battle</t>
-  </si>
-  <si>
-    <t>作战单位；敌友由Faction单独计算。</t>
-  </si>
-  <si>
-    <t>Tile</t>
-  </si>
-  <si>
-    <t>墙或障碍物；不自动代表可摧毁。</t>
-  </si>
-  <si>
-    <t>Grass</t>
-  </si>
-  <si>
-    <t>草标签。</t>
-  </si>
-  <si>
-    <t>Destroyable</t>
-  </si>
-  <si>
-    <t>可摧毁场景物标签；英雄/怪物扣血死亡不要求这个标签。</t>
-  </si>
-  <si>
-    <t>组合值</t>
-  </si>
-  <si>
-    <t>40=Tile|Destroyable；48=Grass|Destroyable</t>
-  </si>
-  <si>
-    <t>整数按位或组合；不同标签位相加得到同样数值。</t>
-  </si>
-  <si>
-    <t>匹配条件</t>
-  </si>
-  <si>
-    <t>同一行所有条件同时满足；同组多行任一匹配</t>
-  </si>
-  <si>
-    <t>Required要求全部位；Excluded出现任意位即拒绝。</t>
-  </si>
-  <si>
-    <t>多行同时匹配</t>
-  </si>
-  <si>
-    <t>BlockProjectile与ApplyHitEvents分别取或</t>
-  </si>
-  <si>
-    <t>一次接触只执行一次HitEvent组和一次碰撞表现；不可按规则行重复执行。</t>
-  </si>
-  <si>
-    <t>阵营关系</t>
-  </si>
-  <si>
-    <t>RelationMask=1敌对；2友善；3不限；0不匹配</t>
-  </si>
-  <si>
-    <t>双方Faction相同不敌对；含NeutralFriendly不敌对；其余不同阵营敌对。默认排除施法者本人。</t>
-  </si>
-  <si>
-    <t>普攻引用</t>
-  </si>
-  <si>
-    <t>10101、40101弹丸 -&gt; 规则组1</t>
-  </si>
-  <si>
-    <t>规则101匹配所有Tile；规则102只匹配敌方Battle；未匹配目标直接穿过。</t>
-  </si>
-  <si>
-    <t>大招引用</t>
-  </si>
-  <si>
-    <t>10102、40102弹丸 -&gt; 规则组2</t>
-  </si>
-  <si>
-    <t>规则201挡不可摧毁墙；202/203/204对可摧毁墙、敌方作战单位、可摧毁草生效并穿过。</t>
-  </si>
-  <si>
-    <t>规则组编号</t>
-  </si>
-  <si>
-    <t>1、2仅为可复用配置ID，不是技能类型枚举</t>
-  </si>
-  <si>
-    <t>任意其他技能也可引用；未来按需要增加更多规则组。</t>
-  </si>
-  <si>
-    <t>普攻1；这两个大招0</t>
-  </si>
-  <si>
-    <t>有效命中次数上限；0不因次数销毁，但仍受BlockProjectile终止。</t>
-  </si>
-  <si>
-    <t>BlocksMovement</t>
-  </si>
-  <si>
-    <t>独立决定活着时是否阻挡英雄移动</t>
-  </si>
-  <si>
-    <t>死亡单位不再阻挡移动或弹丸；不参与弹丸规则匹配。</t>
-  </si>
-  <si>
-    <t>旧数据保留</t>
-  </si>
-  <si>
-    <t>旧BlockMask/TargetMask仅四行清空，其他行原样保留</t>
-  </si>
-  <si>
-    <t>新代码接入前不能把本次源表直接当成已迁移完成的运行配置。</t>
-  </si>
-  <si>
-    <t>技能分页</t>
-  </si>
-  <si>
-    <t>四个技能原有ProjectileId/发射参数已经正确，保持原值</t>
-  </si>
-  <si>
-    <t>未修改其他技能，也未把碰撞规则重复配置到技能层。</t>
-  </si>
-  <si>
-    <t>雪莉大招待填</t>
-  </si>
-  <si>
-    <t>10102弹丸Speed为空，Value及成长为0</t>
-  </si>
-  <si>
-    <t>本次未补数值；当前发射器会拒绝速度0，零伤害不能摧毁墙；击退尚未实现。</t>
-  </si>
-  <si>
-    <t>地形与草</t>
-  </si>
-  <si>
-    <t>本次不新增地形墙/草NPC</t>
-  </si>
-  <si>
-    <t>未来地形查询提供Tile或Grass|Destroyable逻辑标签；草生效处理尚待代码实现。</t>
-  </si>
-  <si>
-    <t>出生点</t>
-  </si>
-  <si>
-    <t>NPC表Faction仍为3，UnitLayerMask=0，不阻挡移动</t>
-  </si>
-  <si>
-    <t>运行时按绑定的红蓝队覆盖阵营；原复活点组件2保留。</t>
-  </si>
-  <si>
-    <t>水晶</t>
-  </si>
-  <si>
-    <t>UnitLayerMask=0，不阻挡移动</t>
-  </si>
-  <si>
-    <t>暂不参与这两组战斗碰撞，后续拾取规则另做。</t>
+    <t xml:space="preserve">模型路径</t>
+  </si>
+  <si>
+    <t xml:space="preserve">碰撞到有效目标或阻挡物时的特效</t>
+  </si>
+  <si>
+    <t xml:space="preserve">到达射程终点、寿命结束时的特效</t>
+  </si>
+  <si>
+    <t xml:space="preserve">碰撞半径（现在默认子弹都是球体方便计算）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">耐久度，即生效几次再销毁，一般需要碰到有效目标才算</t>
+  </si>
+  <si>
+    <t xml:space="preserve">持续时间</t>
+  </si>
+  <si>
+    <t xml:space="preserve">速度</t>
+  </si>
+  <si>
+    <t xml:space="preserve">基础数值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">额外数值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">击中事件1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">击中事件1参数1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">击中事件1参数2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">击中事件2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">击中事件2参数1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">击中事件2参数2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">每枚弹丸对有效目标实际扣血后获得的大招格数；0不充能，与技能类型无关</t>
+  </si>
+  <si>
+    <t xml:space="preserve">碰撞规则组ID，引用BrawlCollisionRule.GroupId。1=墙阻挡/敌方作战单位生效并阻挡；2=不可摧毁墙阻挡/可摧毁场景物和敌方作战单位生效并穿透。仅源表设计，待代码接入。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雪莉的霰弹枪的子弹</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projectile 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hit 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flash 10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雪莉的霰弹枪的大招子弹</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projectile 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hit 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flash 6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">连续发射2次</t>
+  </si>
+  <si>
+    <t xml:space="preserve">卡尔丢出的回旋镖（回弹时不受阻挡影响）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">武士的小刀效果</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柯尔特的手枪子弹</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projectile 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hit 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flash 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">柯尔特的大招子弹</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projectile 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hit 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Flash 14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GroupId</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RequiredLayerMask</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ExcludedLayerMask</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RelationMask</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlockProjectile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ApplyHitEvents</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bool</t>
+  </si>
+  <si>
+    <t xml:space="preserve">规则行ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">规则组ID；同组多行取或</t>
+  </si>
+  <si>
+    <t xml:space="preserve">规则说明</t>
+  </si>
+  <si>
+    <t xml:space="preserve">必须同时具备全部位；0不限</t>
+  </si>
+  <si>
+    <t xml:space="preserve">不能具有任意一位；0不排除</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1敌对；2友善/同阵营；3不限；0不匹配</t>
+  </si>
+  <si>
+    <t xml:space="preserve">匹配后终止弹丸飞行</t>
+  </si>
+  <si>
+    <t xml:space="preserve">匹配后执行弹丸HitEvent组；同次接触仅执行一次</t>
+  </si>
+  <si>
+    <t xml:space="preserve">普攻：所有墙体只阻挡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">普攻：敌方作战单位生效并阻挡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">穿透大招：不可摧毁墙只阻挡</t>
+  </si>
+  <si>
+    <t xml:space="preserve">穿透大招：可摧毁墙生效并穿透</t>
+  </si>
+  <si>
+    <t xml:space="preserve">穿透大招：敌方作战单位生效并穿透</t>
+  </si>
+  <si>
+    <t xml:space="preserve">穿透大招：可摧毁草生效并穿透</t>
+  </si>
+  <si>
+    <t xml:space="preserve">项目</t>
+  </si>
+  <si>
+    <t xml:space="preserve">值或规则</t>
+  </si>
+  <si>
+    <t xml:space="preserve">说明</t>
+  </si>
+  <si>
+    <t xml:space="preserve">实施状态</t>
+  </si>
+  <si>
+    <t xml:space="preserve">仅源表设计，未导出、未接入代码</t>
+  </si>
+  <si>
+    <t xml:space="preserve">当前游戏仍使用旧生成配置；后续需同步代码和Luban表注册再导出。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">英雄标签；英雄组合Hero|Battle=5。英雄表本次不改。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">怪物标签；劫匪组合Monster|Battle=6。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">作战单位；敌友由Faction单独计算。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tile</t>
+  </si>
+  <si>
+    <t xml:space="preserve">墙或障碍物；不自动代表可摧毁。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Grass</t>
+  </si>
+  <si>
+    <t xml:space="preserve">草标签。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Destroyable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">可摧毁场景物标签；英雄/怪物扣血死亡不要求这个标签。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">组合值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40=Tile|Destroyable；48=Grass|Destroyable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">整数按位或组合；不同标签位相加得到同样数值。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">匹配条件</t>
+  </si>
+  <si>
+    <t xml:space="preserve">同一行所有条件同时满足；同组多行任一匹配</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required要求全部位；Excluded出现任意位即拒绝。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">多行同时匹配</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlockProjectile与ApplyHitEvents分别取或</t>
+  </si>
+  <si>
+    <t xml:space="preserve">一次接触只执行一次HitEvent组和一次碰撞表现；不可按规则行重复执行。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">阵营关系</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RelationMask=1敌对；2友善；3不限；0不匹配</t>
+  </si>
+  <si>
+    <t xml:space="preserve">双方Faction相同不敌对；含NeutralFriendly不敌对；其余不同阵营敌对。默认排除施法者本人。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">普攻引用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10101、40101弹丸 -&gt; 规则组1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">规则101匹配所有Tile；规则102只匹配敌方Battle；未匹配目标直接穿过。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">大招引用</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10102、40102弹丸 -&gt; 规则组2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">规则201挡不可摧毁墙；202/203/204对可摧毁墙、敌方作战单位、可摧毁草生效并穿过。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">规则组编号</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1、2仅为可复用配置ID，不是技能类型枚举</t>
+  </si>
+  <si>
+    <t xml:space="preserve">任意其他技能也可引用；未来按需要增加更多规则组。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">普攻1；这两个大招0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有效命中次数上限；0不因次数销毁，但仍受BlockProjectile终止。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BlocksMovement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">独立决定活着时是否阻挡英雄移动</t>
+  </si>
+  <si>
+    <t xml:space="preserve">死亡单位不再阻挡移动或弹丸；不参与弹丸规则匹配。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">旧数据保留</t>
+  </si>
+  <si>
+    <t xml:space="preserve">旧BlockMask/TargetMask仅四行清空，其他行原样保留</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新代码接入前不能把本次源表直接当成已迁移完成的运行配置。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">技能分页</t>
+  </si>
+  <si>
+    <t xml:space="preserve">四个技能原有ProjectileId/发射参数已经正确，保持原值</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未修改其他技能，也未把碰撞规则重复配置到技能层。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">雪莉大招待填</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10102弹丸Speed为空，Value及成长为0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本次未补数值；当前发射器会拒绝速度0，零伤害不能摧毁墙；击退尚未实现。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">地形与草</t>
+  </si>
+  <si>
+    <t xml:space="preserve">本次不新增地形墙/草NPC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">未来地形查询提供Tile或Grass|Destroyable逻辑标签；草生效处理尚待代码实现。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">出生点</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NPC表Faction仍为3，UnitLayerMask=0，不阻挡移动</t>
+  </si>
+  <si>
+    <t xml:space="preserve">运行时按绑定的红蓝队覆盖阵营；原复活点组件2保留。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">水晶</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UnitLayerMask=0，不阻挡移动</t>
+  </si>
+  <si>
+    <t xml:space="preserve">暂不参与这两组战斗碰撞，后续拾取规则另做。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="0" formatCode="General"/>
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="11">
     <font>
       <sz val="10"/>
       <name val="Noto Sans SC"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
@@ -721,7 +749,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF222222"/>
       <name val="Microsoft YaHei"/>
@@ -729,7 +757,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="10"/>
       <color rgb="FF222222"/>
       <name val="Microsoft YaHei"/>
@@ -751,7 +779,7 @@
       <charset val="1"/>
     </font>
     <font>
-      <b/>
+      <b val="true"/>
       <sz val="11"/>
       <name val="Microsoft YaHei"/>
       <family val="2"/>
@@ -797,7 +825,7 @@
     </fill>
   </fills>
   <borders count="1">
-    <border diagonalUp="1" diagonalDown="1">
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
@@ -805,61 +833,109 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="7">
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="1" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="43" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="41" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="44" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="42" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="9" applyNumberFormat="1" fontId="1" applyFont="1" fillId="0" borderId="0" applyBorder="0" applyProtection="0" applyAlignment="0"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="2" applyFont="1" fillId="0" borderId="0" applyBorder="1" applyProtection="1" applyAlignment="1"/>
+  <cellStyleXfs count="21">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="16">
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="0" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="3" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="4" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="3" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1"/>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="5" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="6" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="0" applyFont="1" fillId="0" borderId="0" applyBorder="0" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="4" applyFont="1" fillId="2" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="4" applyFont="1" fillId="4" applyFill="1" borderId="0" applyBorder="1" xfId="6" applyProtection="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="7" applyFont="1" fillId="5" applyFill="1" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" applyNumberFormat="1" fontId="8" applyFont="1" fillId="0" borderId="0" applyBorder="1" xfId="0" applyProtection="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="4" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="2" builtinId="6"/>
-    <cellStyle name="Currency" xfId="3" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="4" builtinId="7"/>
-    <cellStyle name="Percent" xfId="5" builtinId="5"/>
-    <cellStyle name="Normal" xfId="6"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
+    <cellStyle name="Normal" xfId="20"/>
   </cellStyles>
   <colors>
     <indexedColors>
@@ -1094,27 +1170,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr xr2 ">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:T13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="2" width="16" customWidth="1" style="1"/>
-    <col min="3" max="3" width="11.54" customWidth="1" style="1"/>
-    <col min="4" max="5" width="26" customWidth="1" style="2"/>
-    <col min="6" max="6" width="21" customWidth="1" style="1"/>
-    <col min="7" max="7" width="18" customWidth="1" style="1"/>
-    <col min="8" max="10" width="23.5" customWidth="1" style="1"/>
-    <col min="11" max="11" width="19.75" customWidth="1" style="1"/>
-    <col min="12" max="13" width="14.33" customWidth="1" style="1"/>
-    <col min="14" max="17" width="18" customWidth="1" style="1"/>
-    <col min="18" max="18" width="21" customWidth="1" style="1"/>
-    <col min="19" max="21" width="18" customWidth="1" style="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="2" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="1" width="23.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="1" width="19.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="12" style="1" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="14" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="21"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="19" style="1" width="18"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1">
+    <row r="1" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1176,7 +1252,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" ht="26" customHeight="1">
+    <row r="2" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
         <v>20</v>
       </c>
@@ -1238,7 +1314,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" ht="26" customHeight="1">
+    <row r="3" customFormat="false" ht="26" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>24</v>
       </c>
@@ -1266,7 +1342,7 @@
       <c r="S3" s="6"/>
       <c r="T3" s="6"/>
     </row>
-    <row r="4" ht="121.6" customHeight="1">
+    <row r="4" customFormat="false" ht="121.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
         <v>26</v>
       </c>
@@ -1328,8 +1404,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="5" ht="37.3">
-      <c r="B5" s="1">
+    <row r="5" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="n">
         <v>10101</v>
       </c>
       <c r="C5" s="1" t="s">
@@ -1338,57 +1414,57 @@
       <c r="D5" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5" s="2" t="n">
         <v>10101</v>
       </c>
-      <c r="F5" s="1">
+      <c r="F5" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1">
-        <v>0</v>
-      </c>
-      <c r="K5" s="1">
+      <c r="G5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L5" s="1">
+      <c r="L5" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="M5" s="1">
+      <c r="M5" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="N5" s="1">
-        <v>1</v>
-      </c>
-      <c r="O5" s="1">
+      <c r="N5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O5" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="P5" s="1">
+      <c r="P5" s="1" t="n">
         <v>7.67</v>
       </c>
-      <c r="Q5" s="1">
+      <c r="Q5" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="R5" s="1">
-        <v>0</v>
-      </c>
-      <c r="S5" s="1">
-        <v>0</v>
-      </c>
-      <c r="T5" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="37.3">
-      <c r="B6" s="1">
+      <c r="R5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="n">
         <v>10102</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -1397,99 +1473,99 @@
       <c r="D6" s="11" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6" s="2" t="n">
         <v>10102</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="G6" s="1">
-        <v>1</v>
-      </c>
-      <c r="H6" s="1">
-        <v>1</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
-        <v>0</v>
-      </c>
-      <c r="K6" s="1">
-        <v>1</v>
-      </c>
-      <c r="L6" s="1">
+      <c r="G6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L6" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="M6" s="1">
+      <c r="M6" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="N6" s="1">
-        <v>1</v>
-      </c>
-      <c r="O6" s="1">
+      <c r="N6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="P6" s="1">
+      <c r="P6" s="1" t="n">
         <v>7.67</v>
       </c>
-      <c r="Q6" s="1">
+      <c r="Q6" s="1" t="n">
         <v>45</v>
       </c>
-      <c r="R6" s="1">
-        <v>0</v>
-      </c>
-      <c r="S6" s="1">
-        <v>0</v>
-      </c>
-      <c r="T6" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="15">
-      <c r="B7" s="1">
+      <c r="R6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="n">
         <v>10103</v>
       </c>
       <c r="D7" s="11"/>
-      <c r="E7" s="2">
+      <c r="E7" s="2" t="n">
         <v>10103</v>
       </c>
-      <c r="F7" s="1">
+      <c r="F7" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L7" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="M7" s="1">
+      <c r="M7" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="N7" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" ht="15">
-      <c r="B8" s="1">
+      <c r="N7" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="n">
         <v>10104</v>
       </c>
       <c r="D8" s="11"/>
-      <c r="E8" s="2">
+      <c r="E8" s="2" t="n">
         <v>10101</v>
       </c>
-      <c r="F8" s="1">
+      <c r="F8" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="L8" s="1">
+      <c r="L8" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="M8" s="1">
+      <c r="M8" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="N8" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="15">
-      <c r="B9" s="1">
+      <c r="N8" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="n">
         <v>20101</v>
       </c>
       <c r="C9" s="1" t="s">
@@ -1498,39 +1574,39 @@
       <c r="D9" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="2" t="n">
         <v>10101</v>
       </c>
-      <c r="F9" s="1">
+      <c r="F9" s="1" t="n">
         <v>5</v>
       </c>
-      <c r="G9" s="1">
-        <v>1</v>
-      </c>
-      <c r="H9" s="1">
+      <c r="G9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="I9" s="1">
+      <c r="I9" s="1" t="n">
         <v>0.3</v>
       </c>
-      <c r="J9" s="1">
-        <v>0</v>
-      </c>
-      <c r="K9" s="1">
+      <c r="J9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L9" s="1">
+      <c r="L9" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="M9" s="1">
+      <c r="M9" s="1" t="n">
         <v>0.5</v>
       </c>
-      <c r="N9" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="15">
-      <c r="B10" s="1">
+      <c r="N9" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="n">
         <v>100101</v>
       </c>
       <c r="C10" s="1" t="s">
@@ -1539,48 +1615,48 @@
       <c r="D10" s="11" t="s">
         <v>53</v>
       </c>
-      <c r="E10" s="2">
+      <c r="E10" s="2" t="n">
         <v>100101</v>
       </c>
-      <c r="F10" s="1">
-        <v>1</v>
-      </c>
-      <c r="G10" s="1">
+      <c r="F10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="G10" s="1" t="n">
         <v>4</v>
       </c>
-      <c r="K10" s="1">
-        <v>1</v>
-      </c>
-      <c r="L10" s="1">
-        <v>0</v>
-      </c>
-      <c r="M10" s="1">
-        <v>0</v>
-      </c>
-      <c r="N10" s="1">
-        <v>1</v>
-      </c>
-      <c r="O10" s="1">
-        <v>1</v>
-      </c>
-      <c r="P10" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>0</v>
-      </c>
-      <c r="R10" s="1">
-        <v>1</v>
-      </c>
-      <c r="S10" s="1">
-        <v>0</v>
-      </c>
-      <c r="T10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="25.35">
-      <c r="B11" s="1">
+      <c r="K10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="n">
         <v>30101</v>
       </c>
       <c r="C11" s="1" t="s">
@@ -1589,57 +1665,57 @@
       <c r="D11" s="11" t="s">
         <v>55</v>
       </c>
-      <c r="E11" s="2">
+      <c r="E11" s="2" t="n">
         <v>30101</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="1">
+      <c r="G11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="1">
-        <v>1</v>
-      </c>
-      <c r="I11" s="1">
+      <c r="H11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="J11" s="1">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
+      <c r="J11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L11" s="1">
-        <v>1</v>
-      </c>
-      <c r="M11" s="1">
-        <v>1</v>
-      </c>
-      <c r="N11" s="1">
+      <c r="L11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="O11" s="1">
-        <v>1</v>
-      </c>
-      <c r="P11" s="1">
+      <c r="O11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P11" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="Q11" s="1">
+      <c r="Q11" s="1" t="n">
         <v>1.5</v>
       </c>
-      <c r="R11" s="1">
-        <v>0</v>
-      </c>
-      <c r="S11" s="1">
-        <v>0</v>
-      </c>
-      <c r="T11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="37.3">
-      <c r="B12" s="1">
+      <c r="R11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="n">
         <v>40101</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -1648,57 +1724,57 @@
       <c r="D12" s="11" t="s">
         <v>57</v>
       </c>
-      <c r="E12" s="2">
+      <c r="E12" s="2" t="n">
         <v>40101</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="G12" s="1">
+      <c r="G12" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H12" s="1">
-        <v>1</v>
-      </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
+      <c r="H12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1" t="n">
         <v>0.16</v>
       </c>
-      <c r="K12" s="1">
+      <c r="K12" s="1" t="n">
         <v>3</v>
       </c>
-      <c r="L12" s="1">
+      <c r="L12" s="1" t="n">
         <v>1.6</v>
       </c>
-      <c r="M12" s="1">
+      <c r="M12" s="1" t="n">
         <v>0.8</v>
       </c>
-      <c r="N12" s="1">
-        <v>1</v>
-      </c>
-      <c r="O12" s="1">
-        <v>1</v>
-      </c>
-      <c r="P12" s="1">
+      <c r="N12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P12" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="Q12" s="1">
+      <c r="Q12" s="1" t="n">
         <v>0.7</v>
       </c>
-      <c r="R12" s="1">
-        <v>0</v>
-      </c>
-      <c r="S12" s="1">
-        <v>0</v>
-      </c>
-      <c r="T12" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="37.3">
-      <c r="B13" s="1">
+      <c r="R12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="n">
         <v>40102</v>
       </c>
       <c r="C13" s="1" t="s">
@@ -1707,52 +1783,52 @@
       <c r="D13" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="E13" s="2">
+      <c r="E13" s="2" t="n">
         <v>40102</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="G13" s="1">
+      <c r="G13" s="1" t="n">
         <v>2</v>
       </c>
-      <c r="H13" s="1">
-        <v>1</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
+      <c r="H13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1" t="n">
         <v>0.08333</v>
       </c>
-      <c r="K13" s="1">
-        <v>1</v>
-      </c>
-      <c r="L13" s="1">
-        <v>0</v>
-      </c>
-      <c r="M13" s="1">
-        <v>1</v>
-      </c>
-      <c r="N13" s="1">
-        <v>1</v>
-      </c>
-      <c r="O13" s="1">
-        <v>1</v>
-      </c>
-      <c r="P13" s="1">
+      <c r="K13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="P13" s="1" t="n">
         <v>12</v>
       </c>
-      <c r="Q13" s="1">
-        <v>1</v>
-      </c>
-      <c r="R13" s="1">
-        <v>0</v>
-      </c>
-      <c r="S13" s="1">
-        <v>0</v>
-      </c>
-      <c r="T13" s="1">
+      <c r="Q13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="1" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1768,29 +1844,29 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr xr2 ">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:T13"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="2" width="16" customWidth="1" style="1"/>
-    <col min="3" max="6" width="26" customWidth="1" style="2"/>
-    <col min="7" max="7" width="16.27" customWidth="1" style="2"/>
-    <col min="8" max="8" width="28.79" customWidth="1" style="1"/>
-    <col min="9" max="11" width="23.23" customWidth="1" style="1"/>
-    <col min="12" max="12" width="22.12" customWidth="1" style="1"/>
-    <col min="13" max="13" width="16.43" customWidth="1" style="1"/>
-    <col min="14" max="14" width="23.23" customWidth="1" style="1"/>
-    <col min="15" max="15" width="22.12" customWidth="1" style="1"/>
-    <col min="16" max="16" width="16.43" customWidth="1" style="1"/>
-    <col min="17" max="17" width="23.23" customWidth="1" style="1"/>
-    <col min="18" max="18" width="22.12" customWidth="1" style="1"/>
-    <col min="20" max="20" width="45" customWidth="1" style="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="2" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="16.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="28.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="1" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="22.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="1" width="22.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="16.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="1" width="23.23"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="1" width="22.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="1" width="45"/>
   </cols>
   <sheetData>
-    <row r="1" ht="16.4">
+    <row r="1" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1852,7 +1928,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="2" ht="16.4">
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
         <v>20</v>
       </c>
@@ -1914,7 +1990,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="3" ht="16.4">
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
         <v>24</v>
       </c>
@@ -1946,7 +2022,7 @@
       <c r="S3" s="6"/>
       <c r="T3" s="6"/>
     </row>
-    <row r="4" ht="105.95">
+    <row r="4" customFormat="false" ht="105.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
         <v>26</v>
       </c>
@@ -2008,8 +2084,8 @@
         <v>94</v>
       </c>
     </row>
-    <row r="5" ht="13.4">
-      <c r="B5" s="1">
+    <row r="5" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="1" t="n">
         <v>10101</v>
       </c>
       <c r="C5" s="11" t="s">
@@ -2024,51 +2100,51 @@
       <c r="F5" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="G5" s="11">
+      <c r="G5" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="H5" s="1">
-        <v>1</v>
-      </c>
-      <c r="I5" s="1">
-        <v>0</v>
-      </c>
-      <c r="J5" s="1">
+      <c r="H5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="K5" s="1">
+      <c r="K5" s="1" t="n">
         <v>300</v>
       </c>
-      <c r="L5" s="1">
+      <c r="L5" s="1" t="n">
         <v>30</v>
       </c>
-      <c r="M5" s="1">
-        <v>1</v>
-      </c>
-      <c r="N5" s="1">
-        <v>0</v>
-      </c>
-      <c r="O5" s="1">
-        <v>0</v>
-      </c>
-      <c r="P5" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q5" s="1">
-        <v>0</v>
-      </c>
-      <c r="R5" s="1">
-        <v>0</v>
-      </c>
-      <c r="S5" s="1">
+      <c r="M5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="T5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" ht="13.4">
-      <c r="B6" s="1">
+      <c r="T5" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="1" t="n">
         <v>10102</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -2083,258 +2159,258 @@
       <c r="F6" s="11" t="s">
         <v>102</v>
       </c>
-      <c r="G6" s="11">
+      <c r="G6" s="11" t="n">
         <v>0.06</v>
       </c>
-      <c r="H6" s="1">
-        <v>0</v>
-      </c>
-      <c r="I6" s="1">
-        <v>0</v>
-      </c>
-      <c r="J6" s="1">
+      <c r="H6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="n">
         <v>9</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K6" s="1" t="n">
         <v>288</v>
       </c>
-      <c r="L6" s="1">
+      <c r="L6" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="M6" s="1">
-        <v>1</v>
-      </c>
-      <c r="N6" s="1">
-        <v>0</v>
-      </c>
-      <c r="O6" s="1">
-        <v>0</v>
-      </c>
-      <c r="P6" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q6" s="1">
-        <v>0</v>
-      </c>
-      <c r="R6" s="1">
-        <v>0</v>
-      </c>
-      <c r="S6" s="1">
+      <c r="M6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="T6" s="1">
+      <c r="T6" s="1" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="7" ht="13.4">
-      <c r="B7" s="1">
+    <row r="7" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="1" t="n">
         <v>10103</v>
       </c>
       <c r="G7" s="11"/>
-      <c r="K7" s="1">
-        <v>0</v>
-      </c>
-      <c r="L7" s="1">
-        <v>0</v>
-      </c>
-      <c r="M7" s="1">
-        <v>1</v>
-      </c>
-      <c r="N7" s="1">
-        <v>0</v>
-      </c>
-      <c r="O7" s="1">
-        <v>0</v>
-      </c>
-      <c r="P7" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q7" s="1">
-        <v>0</v>
-      </c>
-      <c r="R7" s="1">
-        <v>0</v>
-      </c>
-      <c r="S7" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="13.4">
-      <c r="B8" s="1">
+      <c r="K7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="1" t="n">
         <v>10104</v>
       </c>
       <c r="G8" s="11"/>
-      <c r="K8" s="1">
-        <v>0</v>
-      </c>
-      <c r="L8" s="1">
-        <v>0</v>
-      </c>
-      <c r="M8" s="1">
-        <v>1</v>
-      </c>
-      <c r="N8" s="1">
-        <v>0</v>
-      </c>
-      <c r="O8" s="1">
-        <v>0</v>
-      </c>
-      <c r="P8" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="1">
-        <v>0</v>
-      </c>
-      <c r="R8" s="1">
-        <v>0</v>
-      </c>
-      <c r="S8" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" ht="13.4">
-      <c r="B9" s="1">
+      <c r="K8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="1" t="n">
         <v>20101</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G9" s="11">
+      <c r="G9" s="11" t="n">
         <v>0.05</v>
       </c>
-      <c r="H9" s="1">
-        <v>1</v>
-      </c>
-      <c r="I9" s="1">
-        <v>0</v>
-      </c>
-      <c r="J9" s="1">
+      <c r="H9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="n">
         <v>8</v>
       </c>
-      <c r="K9" s="1">
-        <v>0</v>
-      </c>
-      <c r="L9" s="1">
-        <v>0</v>
-      </c>
-      <c r="M9" s="1">
-        <v>1</v>
-      </c>
-      <c r="N9" s="1">
-        <v>0</v>
-      </c>
-      <c r="O9" s="1">
-        <v>0</v>
-      </c>
-      <c r="P9" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q9" s="1">
-        <v>0</v>
-      </c>
-      <c r="R9" s="1">
-        <v>0</v>
-      </c>
-      <c r="S9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="25.35">
-      <c r="B10" s="1">
+      <c r="K9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="1" t="n">
         <v>100101</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="G10" s="2">
-        <v>1</v>
-      </c>
-      <c r="H10" s="1">
-        <v>0</v>
-      </c>
-      <c r="I10" s="1">
-        <v>0</v>
-      </c>
-      <c r="J10" s="1">
+      <c r="G10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="1" t="n">
         <v>6</v>
       </c>
-      <c r="K10" s="1">
+      <c r="K10" s="1" t="n">
         <v>820</v>
       </c>
-      <c r="L10" s="1">
+      <c r="L10" s="1" t="n">
         <v>82</v>
       </c>
-      <c r="M10" s="1">
-        <v>1</v>
-      </c>
-      <c r="N10" s="1">
-        <v>0</v>
-      </c>
-      <c r="O10" s="1">
-        <v>0</v>
-      </c>
-      <c r="P10" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q10" s="1">
-        <v>0</v>
-      </c>
-      <c r="R10" s="1">
-        <v>0</v>
-      </c>
-      <c r="S10" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="13.4">
-      <c r="B11" s="1">
+      <c r="M10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="1" t="n">
         <v>30101</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="G11" s="2">
+      <c r="G11" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="H11" s="1">
-        <v>0</v>
-      </c>
-      <c r="I11" s="1">
-        <v>1</v>
-      </c>
-      <c r="J11" s="1">
-        <v>0</v>
-      </c>
-      <c r="K11" s="1">
-        <v>0</v>
-      </c>
-      <c r="L11" s="1">
-        <v>0</v>
-      </c>
-      <c r="M11" s="1">
-        <v>1</v>
-      </c>
-      <c r="N11" s="1">
-        <v>0</v>
-      </c>
-      <c r="O11" s="1">
-        <v>0</v>
-      </c>
-      <c r="P11" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q11" s="1">
-        <v>0</v>
-      </c>
-      <c r="R11" s="1">
-        <v>0</v>
-      </c>
-      <c r="S11" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" ht="13.4">
-      <c r="B12" s="1">
+      <c r="H11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" s="1" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="1" t="n">
         <v>40101</v>
       </c>
       <c r="C12" s="2" t="s">
@@ -2349,51 +2425,51 @@
       <c r="F12" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="G12" s="2">
+      <c r="G12" s="2" t="n">
         <v>0.04</v>
       </c>
-      <c r="H12" s="1">
-        <v>1</v>
-      </c>
-      <c r="I12" s="1">
-        <v>0</v>
-      </c>
-      <c r="J12" s="1">
+      <c r="H12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="K12" s="1">
+      <c r="K12" s="1" t="n">
         <v>360</v>
       </c>
-      <c r="L12" s="1">
+      <c r="L12" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="M12" s="1">
-        <v>1</v>
-      </c>
-      <c r="N12" s="1">
-        <v>0</v>
-      </c>
-      <c r="O12" s="1">
-        <v>0</v>
-      </c>
-      <c r="P12" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="1">
-        <v>0</v>
-      </c>
-      <c r="R12" s="1">
-        <v>0</v>
-      </c>
-      <c r="S12" s="1">
+      <c r="M12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="T12" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" ht="13.4">
-      <c r="B13" s="1">
+      <c r="T12" s="1" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="1" t="n">
         <v>40102</v>
       </c>
       <c r="C13" s="2" t="s">
@@ -2408,46 +2484,46 @@
       <c r="F13" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="G13" s="2">
+      <c r="G13" s="2" t="n">
         <v>0.06</v>
       </c>
-      <c r="H13" s="1">
-        <v>0</v>
-      </c>
-      <c r="I13" s="1">
-        <v>0</v>
-      </c>
-      <c r="J13" s="1">
+      <c r="H13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="1" t="n">
         <v>10</v>
       </c>
-      <c r="K13" s="1">
+      <c r="K13" s="1" t="n">
         <v>320</v>
       </c>
-      <c r="L13" s="1">
+      <c r="L13" s="1" t="n">
         <v>32</v>
       </c>
-      <c r="M13" s="1">
-        <v>1</v>
-      </c>
-      <c r="N13" s="1">
-        <v>0</v>
-      </c>
-      <c r="O13" s="1">
-        <v>0</v>
-      </c>
-      <c r="P13" s="1">
-        <v>0</v>
-      </c>
-      <c r="Q13" s="1">
-        <v>0</v>
-      </c>
-      <c r="R13" s="1">
-        <v>0</v>
-      </c>
-      <c r="S13" s="1">
+      <c r="M13" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="S13" s="1" t="n">
         <v>0.1</v>
       </c>
-      <c r="T13" s="1">
+      <c r="T13" s="1" t="n">
         <v>2</v>
       </c>
     </row>
@@ -2463,24 +2539,24 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr xr2 ">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="10.66" customWidth="1" style="1"/>
-    <col min="2" max="2" width="11.12" customWidth="1" style="1"/>
-    <col min="3" max="3" width="30.7" customWidth="1" style="1"/>
-    <col min="4" max="4" width="42.62" customWidth="1" style="1"/>
-    <col min="5" max="6" width="35.17" customWidth="1" style="1"/>
-    <col min="7" max="7" width="49" customWidth="1" style="1"/>
-    <col min="8" max="8" width="25.17" customWidth="1" style="1"/>
-    <col min="9" max="9" width="61.22" customWidth="1" style="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="10.66"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="30.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="42.62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="35.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="25.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="61.22"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -2509,7 +2585,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="2" ht="15">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
         <v>20</v>
       </c>
@@ -2538,7 +2614,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="3" ht="15">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="14" t="s">
         <v>24</v>
       </c>
@@ -2553,7 +2629,7 @@
       <c r="H3" s="14"/>
       <c r="I3" s="14"/>
     </row>
-    <row r="4" ht="16.4">
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
         <v>26</v>
       </c>
@@ -2582,177 +2658,177 @@
         <v>128</v>
       </c>
     </row>
-    <row r="5" ht="15">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15"/>
-      <c r="B5" s="15">
+      <c r="B5" s="15" t="n">
         <v>101</v>
       </c>
-      <c r="C5" s="15">
+      <c r="C5" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D5" s="15" t="s">
         <v>129</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="F5" s="15">
-        <v>0</v>
-      </c>
-      <c r="G5" s="15">
+      <c r="F5" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H5" s="15" t="b">
-        <f>TRUE()</f>
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I5" s="15" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" ht="15">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15"/>
-      <c r="B6" s="15">
+      <c r="B6" s="15" t="n">
         <v>102</v>
       </c>
-      <c r="C6" s="15">
+      <c r="C6" s="15" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="F6" s="15">
-        <v>0</v>
-      </c>
-      <c r="G6" s="15">
+      <c r="F6" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H6" s="15" t="b">
-        <f>TRUE()</f>
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I6" s="15" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" ht="15">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15"/>
-      <c r="B7" s="15">
+      <c r="B7" s="15" t="n">
         <v>201</v>
       </c>
-      <c r="C7" s="15">
+      <c r="C7" s="15" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="15" t="n">
         <v>8</v>
       </c>
-      <c r="F7" s="15">
+      <c r="F7" s="15" t="n">
         <v>32</v>
       </c>
-      <c r="G7" s="15">
+      <c r="G7" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H7" s="15" t="b">
-        <f>TRUE()</f>
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
       <c r="I7" s="15" t="b">
-        <f>FALSE()</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="15">
+        <f aca="false">FALSE()</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15"/>
-      <c r="B8" s="15">
+      <c r="B8" s="15" t="n">
         <v>202</v>
       </c>
-      <c r="C8" s="15">
+      <c r="C8" s="15" t="n">
         <v>2</v>
       </c>
       <c r="D8" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="E8" s="15">
+      <c r="E8" s="15" t="n">
         <v>40</v>
       </c>
-      <c r="F8" s="15">
-        <v>0</v>
-      </c>
-      <c r="G8" s="15">
+      <c r="F8" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H8" s="15" t="b">
-        <f>FALSE()</f>
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="I8" s="15" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" ht="15">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15"/>
-      <c r="B9" s="15">
+      <c r="B9" s="15" t="n">
         <v>203</v>
       </c>
-      <c r="C9" s="15">
+      <c r="C9" s="15" t="n">
         <v>2</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="E9" s="15">
+      <c r="E9" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="15">
-        <v>0</v>
-      </c>
-      <c r="G9" s="15">
+      <c r="F9" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="15" t="n">
         <v>1</v>
       </c>
       <c r="H9" s="15" t="b">
-        <f>FALSE()</f>
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="I9" s="15" t="b">
-        <f>TRUE()</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" ht="15">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15"/>
-      <c r="B10" s="15">
+      <c r="B10" s="15" t="n">
         <v>204</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="15" t="n">
         <v>2</v>
       </c>
       <c r="D10" s="15" t="s">
         <v>134</v>
       </c>
-      <c r="E10" s="15">
+      <c r="E10" s="15" t="n">
         <v>48</v>
       </c>
-      <c r="F10" s="15">
-        <v>0</v>
-      </c>
-      <c r="G10" s="15">
+      <c r="F10" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="15" t="n">
         <v>3</v>
       </c>
       <c r="H10" s="15" t="b">
-        <f>FALSE()</f>
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="I10" s="15" t="b">
-        <f>TRUE()</f>
+        <f aca="false">TRUE()</f>
         <v>1</v>
       </c>
     </row>
@@ -2768,19 +2844,19 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr xr2 ">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="19.38" customWidth="1" style="1"/>
-    <col min="2" max="2" width="64.46" customWidth="1" style="1"/>
-    <col min="3" max="3" width="110.66" customWidth="1" style="1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="19.38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="64.46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="110.66"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="14" t="s">
         <v>135</v>
       </c>
@@ -2791,7 +2867,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="2" ht="16.4">
+    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="15" t="s">
         <v>138</v>
       </c>
@@ -2802,73 +2878,73 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" ht="16.4">
+    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="B3" s="15">
+      <c r="B3" s="15" t="n">
         <v>1</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="4" ht="16.4">
+    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="B4" s="15">
+      <c r="B4" s="15" t="n">
         <v>2</v>
       </c>
       <c r="C4" s="15" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="5" ht="16.4">
+    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="15" t="s">
         <v>145</v>
       </c>
-      <c r="B5" s="15">
+      <c r="B5" s="15" t="n">
         <v>4</v>
       </c>
       <c r="C5" s="15" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="6" ht="15">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="15" t="n">
         <v>8</v>
       </c>
       <c r="C6" s="15" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="7" ht="15">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="15" t="s">
         <v>149</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="15" t="n">
         <v>16</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="8" ht="16.4">
+    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="B8" s="15">
+      <c r="B8" s="15" t="n">
         <v>32</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="9" ht="16.4">
+    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="15" t="s">
         <v>153</v>
       </c>
@@ -2879,7 +2955,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="10" ht="16.4">
+    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="15" t="s">
         <v>156</v>
       </c>
@@ -2890,7 +2966,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="11" ht="16.4">
+    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="15" t="s">
         <v>159</v>
       </c>
@@ -2901,7 +2977,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="12" ht="16.4">
+    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="15" t="s">
         <v>162</v>
       </c>
@@ -2912,7 +2988,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="13" ht="16.4">
+    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="15" t="s">
         <v>165</v>
       </c>
@@ -2923,7 +2999,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="14" ht="16.4">
+    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="15" t="s">
         <v>168</v>
       </c>
@@ -2934,7 +3010,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="15" ht="16.4">
+    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="15" t="s">
         <v>171</v>
       </c>
@@ -2945,7 +3021,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="16" ht="16.4">
+    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="15" t="s">
         <v>64</v>
       </c>
@@ -2956,7 +3032,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="17" ht="15">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="15" t="s">
         <v>176</v>
       </c>
@@ -2967,7 +3043,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="18" ht="16.4">
+    <row r="18" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="15" t="s">
         <v>179</v>
       </c>
@@ -2978,7 +3054,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="19" ht="16.4">
+    <row r="19" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="15" t="s">
         <v>182</v>
       </c>
@@ -2989,7 +3065,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="20" ht="16.4">
+    <row r="20" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="15" t="s">
         <v>185</v>
       </c>
@@ -3000,7 +3076,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="21" ht="16.4">
+    <row r="21" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="15" t="s">
         <v>188</v>
       </c>
@@ -3011,7 +3087,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="22" ht="16.4">
+    <row r="22" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="15" t="s">
         <v>191</v>
       </c>
@@ -3022,7 +3098,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="23" ht="16.4">
+    <row r="23" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="15" t="s">
         <v>194</v>
       </c>
@@ -3042,9 +3118,4 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
-For more information about EPPlus, see https://epplussoftware.com/
-
 </file>
--- a/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlSkill.xlsx
+++ b/Packages/cn.etetet.brawl/Luban/Config/Datas/BrawlSkill.xlsx
@@ -1439,7 +1439,7 @@
         <v>1.5</v>
       </c>
       <c r="M5" s="1" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N5" s="1" t="n">
         <v>1</v>
